--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92675</v>
+        <v>92678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136139710</v>
       </c>
       <c r="B5" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         <v>135904733</v>
       </c>
       <c r="B42" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>135904732</v>
       </c>
       <c r="B50" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>136572893</v>
       </c>
       <c r="B61" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 24249-2024 artfynd.xlsx
+++ b/artfynd/A 24249-2024 artfynd.xlsx
@@ -5071,7 +5071,7 @@
         <v>136572862</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>136572863</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
